--- a/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Pictures 20260424080239.xlsx
+++ b/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/Pictures 20260424080239.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emma\Desktop\evidence\FileSystem\metadata\Parsed Metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/DFIR-Simulation-Platform/Windows_Ransomware_Intrusion/evidence/FileSystem/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFAAC809-2317-4CC1-AC19-17BD6138D8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F4F36A-076D-724B-A928-7AA49E54EBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8508" yWindow="0" windowWidth="14628" windowHeight="12336" xr2:uid="{D5E5B2C0-193B-4A0B-94DF-58C77E9D8AD4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23120" windowHeight="11420" xr2:uid="{D5E5B2C0-193B-4A0B-94DF-58C77E9D8AD4}"/>
   </bookViews>
   <sheets>
     <sheet name="Pictures 20260424080239" sheetId="1" r:id="rId1"/>
@@ -624,6 +624,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{003355DD-E3D2-5A4B-AB41-E2C206B878A2}" name="Table1" displayName="Table1" ref="A1:H4" totalsRowShown="0">
+  <autoFilter ref="A1:H4" xr:uid="{003355DD-E3D2-5A4B-AB41-E2C206B878A2}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{D4645F72-61DD-8D4F-92BC-C3D81A133FD0}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{19170CE2-6802-2547-A3C9-0D87EBE8801C}" name="Modified Time"/>
+    <tableColumn id="3" xr3:uid="{9E76DA83-DCC5-6041-8F5E-BCE37C623CF2}" name="Change Time"/>
+    <tableColumn id="4" xr3:uid="{8B5E5508-3E59-6E41-9656-B92F5584A352}" name="Access Time"/>
+    <tableColumn id="5" xr3:uid="{EACF95A9-D10F-8849-8E26-0A956547D0B4}" name="Created Time"/>
+    <tableColumn id="6" xr3:uid="{36FD2B26-D6AB-DA49-88AE-8AF8FF1509E5}" name="Size"/>
+    <tableColumn id="7" xr3:uid="{8177AF84-7B29-8242-B368-71871D0C2718}" name="Location"/>
+    <tableColumn id="8" xr3:uid="{00CF5B49-1CC6-E445-AC86-DC50C83E3DC2}" name="Extension"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -944,16 +961,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD6C429-97D7-4F8B-96C8-8B0D174385FF}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="59.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="80" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="73.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -979,7 +996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1005,7 +1022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1031,7 +1048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1059,5 +1076,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>